--- a/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C247FD00-043C-4B9F-88E3-9E96FA58E541}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD38D26-26F0-4A75-9F96-12854BD45870}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD38D26-26F0-4A75-9F96-12854BD45870}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80E499A-27F2-43A6-A163-483F64EAAD50}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="77">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -261,6 +261,9 @@
   </si>
   <si>
     <t>MAY 2026</t>
+  </si>
+  <si>
+    <t>05/16/2026</t>
   </si>
 </sst>
 </file>
@@ -2371,8 +2374,8 @@
       <c r="B7" s="23">
         <v>1</v>
       </c>
-      <c r="C7" s="19">
-        <v>46361</v>
+      <c r="C7" s="19" t="s">
+        <v>76</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>68</v>
@@ -2381,22 +2384,27 @@
       <c r="F7" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G7" s="20"/>
+      <c r="G7" s="20">
+        <v>518642084</v>
+      </c>
       <c r="H7" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I7" s="21"/>
+      <c r="I7" s="21">
+        <f>1261704-123701.1</f>
+        <v>1138002.8999999999</v>
+      </c>
       <c r="K7" s="21">
         <f>M7*12</f>
-        <v>0</v>
+        <v>121928.88214285714</v>
       </c>
       <c r="L7" s="27">
         <f>I7-K7</f>
-        <v>0</v>
+        <v>1016074.0178571427</v>
       </c>
       <c r="M7" s="33">
         <f>I7/112</f>
-        <v>0</v>
+        <v>10160.740178571428</v>
       </c>
       <c r="N7" s="26"/>
       <c r="O7" s="26"/>
@@ -3129,20 +3137,20 @@
       <c r="G32"/>
       <c r="I32" s="46">
         <f>SUM(I7:I31)</f>
-        <v>0</v>
+        <v>1138002.8999999999</v>
       </c>
       <c r="J32" s="47"/>
       <c r="K32" s="46">
         <f>SUM(K7:K31)</f>
-        <v>0</v>
+        <v>121928.88214285714</v>
       </c>
       <c r="L32" s="46">
         <f>SUM(L7:L31)</f>
-        <v>0</v>
+        <v>1016074.0178571427</v>
       </c>
       <c r="M32" s="48">
         <f>SUM(M7:M31)</f>
-        <v>0</v>
+        <v>10160.740178571428</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80E499A-27F2-43A6-A163-483F64EAAD50}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96D1C4A-82C8-49D6-B954-72036AC556A4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="78">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -264,6 +264,9 @@
   </si>
   <si>
     <t>05/16/2026</t>
+  </si>
+  <si>
+    <t>05/18/2026</t>
   </si>
 </sst>
 </file>
@@ -2418,7 +2421,9 @@
         <f>B7+1</f>
         <v>2</v>
       </c>
-      <c r="C8" s="19"/>
+      <c r="C8" s="19" t="s">
+        <v>77</v>
+      </c>
       <c r="D8" s="20" t="s">
         <v>68</v>
       </c>
@@ -2426,22 +2431,27 @@
       <c r="F8" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G8" s="20"/>
+      <c r="G8" s="20">
+        <v>51864</v>
+      </c>
       <c r="H8" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I8" s="21"/>
+      <c r="I8" s="21">
+        <f>1397196-60845.09</f>
+        <v>1336350.9099999999</v>
+      </c>
       <c r="K8" s="21">
         <f>M8*12</f>
-        <v>0</v>
+        <v>143180.45464285713</v>
       </c>
       <c r="L8" s="27">
         <f>I8-K8</f>
-        <v>0</v>
+        <v>1193170.4553571427</v>
       </c>
       <c r="M8" s="33">
         <f t="shared" ref="M8:M26" si="0">I8/112</f>
-        <v>0</v>
+        <v>11931.704553571428</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -3137,20 +3147,20 @@
       <c r="G32"/>
       <c r="I32" s="46">
         <f>SUM(I7:I31)</f>
-        <v>1138002.8999999999</v>
+        <v>2474353.8099999996</v>
       </c>
       <c r="J32" s="47"/>
       <c r="K32" s="46">
         <f>SUM(K7:K31)</f>
-        <v>121928.88214285714</v>
+        <v>265109.33678571426</v>
       </c>
       <c r="L32" s="46">
         <f>SUM(L7:L31)</f>
-        <v>1016074.0178571427</v>
+        <v>2209244.4732142854</v>
       </c>
       <c r="M32" s="48">
         <f>SUM(M7:M31)</f>
-        <v>10160.740178571428</v>
+        <v>22092.444732142856</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96D1C4A-82C8-49D6-B954-72036AC556A4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{436CB60C-73F5-4552-B737-96D91BBE36E3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="79">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -267,6 +267,9 @@
   </si>
   <si>
     <t>05/18/2026</t>
+  </si>
+  <si>
+    <t>05/19/2026</t>
   </si>
 </sst>
 </file>
@@ -2463,7 +2466,9 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C9" s="19"/>
+      <c r="C9" s="19" t="s">
+        <v>78</v>
+      </c>
       <c r="D9" s="20" t="s">
         <v>68</v>
       </c>
@@ -2471,22 +2476,27 @@
       <c r="F9" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G9" s="20"/>
+      <c r="G9" s="20">
+        <v>518652028</v>
+      </c>
       <c r="H9" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I9" s="21"/>
+      <c r="I9" s="21">
+        <f>1397196-30845.04</f>
+        <v>1366350.96</v>
+      </c>
       <c r="K9" s="21">
         <f t="shared" ref="K9:K26" si="2">M9*12</f>
-        <v>0</v>
+        <v>146394.7457142857</v>
       </c>
       <c r="L9" s="27">
         <f t="shared" ref="L9:L26" si="3">I9-K9</f>
-        <v>0</v>
+        <v>1219956.2142857143</v>
       </c>
       <c r="M9" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12199.562142857143</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -3147,20 +3157,20 @@
       <c r="G32"/>
       <c r="I32" s="46">
         <f>SUM(I7:I31)</f>
-        <v>2474353.8099999996</v>
+        <v>3840704.7699999996</v>
       </c>
       <c r="J32" s="47"/>
       <c r="K32" s="46">
         <f>SUM(K7:K31)</f>
-        <v>265109.33678571426</v>
+        <v>411504.08249999996</v>
       </c>
       <c r="L32" s="46">
         <f>SUM(L7:L31)</f>
-        <v>2209244.4732142854</v>
+        <v>3429200.6875</v>
       </c>
       <c r="M32" s="48">
         <f>SUM(M7:M31)</f>
-        <v>22092.444732142856</v>
+        <v>34292.006874999999</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{436CB60C-73F5-4552-B737-96D91BBE36E3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27673EC-E20E-4ECA-89B4-0083EDCAE508}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="80">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -270,6 +270,9 @@
   </si>
   <si>
     <t>05/19/2026</t>
+  </si>
+  <si>
+    <t>05/20/2026</t>
   </si>
 </sst>
 </file>
@@ -2508,7 +2511,9 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="C10" s="19"/>
+      <c r="C10" s="19" t="s">
+        <v>79</v>
+      </c>
       <c r="D10" s="20" t="s">
         <v>68</v>
       </c>
@@ -2516,22 +2521,27 @@
       <c r="F10" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G10" s="20"/>
+      <c r="G10" s="20">
+        <v>518655849</v>
+      </c>
       <c r="H10" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I10" s="21"/>
+      <c r="I10" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K10" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L10" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M10" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -3157,20 +3167,20 @@
       <c r="G32"/>
       <c r="I32" s="46">
         <f>SUM(I7:I31)</f>
-        <v>3840704.7699999996</v>
+        <v>5177055.7299999995</v>
       </c>
       <c r="J32" s="47"/>
       <c r="K32" s="46">
         <f>SUM(K7:K31)</f>
-        <v>411504.08249999996</v>
+        <v>554684.54249999998</v>
       </c>
       <c r="L32" s="46">
         <f>SUM(L7:L31)</f>
-        <v>3429200.6875</v>
+        <v>4622371.1875</v>
       </c>
       <c r="M32" s="48">
         <f>SUM(M7:M31)</f>
-        <v>34292.006874999999</v>
+        <v>46223.711875000001</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A27673EC-E20E-4ECA-89B4-0083EDCAE508}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F5C74F-42BD-434B-B4AF-B5454E21C0E1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="81">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -273,6 +273,9 @@
   </si>
   <si>
     <t>05/20/2026</t>
+  </si>
+  <si>
+    <t>05/21/2026</t>
   </si>
 </sst>
 </file>
@@ -2553,7 +2556,9 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="C11" s="19"/>
+      <c r="C11" s="19" t="s">
+        <v>80</v>
+      </c>
       <c r="D11" s="20" t="s">
         <v>68</v>
       </c>
@@ -2561,22 +2566,27 @@
       <c r="F11" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G11" s="20"/>
+      <c r="G11" s="20">
+        <v>518659757</v>
+      </c>
       <c r="H11" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I11" s="21"/>
+      <c r="I11" s="21">
+        <f>1397196-70830.93</f>
+        <v>1326365.07</v>
+      </c>
       <c r="K11" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>142110.54321428572</v>
       </c>
       <c r="L11" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1184254.5267857143</v>
       </c>
       <c r="M11" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11842.545267857144</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -3167,20 +3177,20 @@
       <c r="G32"/>
       <c r="I32" s="46">
         <f>SUM(I7:I31)</f>
-        <v>5177055.7299999995</v>
+        <v>6503420.7999999998</v>
       </c>
       <c r="J32" s="47"/>
       <c r="K32" s="46">
         <f>SUM(K7:K31)</f>
-        <v>554684.54249999998</v>
+        <v>696795.08571428573</v>
       </c>
       <c r="L32" s="46">
         <f>SUM(L7:L31)</f>
-        <v>4622371.1875</v>
+        <v>5806625.7142857146</v>
       </c>
       <c r="M32" s="48">
         <f>SUM(M7:M31)</f>
-        <v>46223.711875000001</v>
+        <v>58066.257142857146</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F5C74F-42BD-434B-B4AF-B5454E21C0E1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC0B6FA-7364-4E5B-95CC-1EAFAB2BD257}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="82">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -276,6 +276,9 @@
   </si>
   <si>
     <t>05/21/2026</t>
+  </si>
+  <si>
+    <t>05/23/2026</t>
   </si>
 </sst>
 </file>
@@ -2598,7 +2601,9 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="C12" s="19"/>
+      <c r="C12" s="19" t="s">
+        <v>81</v>
+      </c>
       <c r="D12" s="20" t="s">
         <v>68</v>
       </c>
@@ -2606,22 +2611,27 @@
       <c r="F12" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G12" s="20"/>
+      <c r="G12" s="20">
+        <v>518667896</v>
+      </c>
       <c r="H12" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I12" s="21"/>
+      <c r="I12" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K12" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L12" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M12" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -3177,20 +3187,20 @@
       <c r="G32"/>
       <c r="I32" s="46">
         <f>SUM(I7:I31)</f>
-        <v>6503420.7999999998</v>
+        <v>7839771.7599999998</v>
       </c>
       <c r="J32" s="47"/>
       <c r="K32" s="46">
         <f>SUM(K7:K31)</f>
-        <v>696795.08571428573</v>
+        <v>839975.54571428569</v>
       </c>
       <c r="L32" s="46">
         <f>SUM(L7:L31)</f>
-        <v>5806625.7142857146</v>
+        <v>6999796.2142857146</v>
       </c>
       <c r="M32" s="48">
         <f>SUM(M7:M31)</f>
-        <v>58066.257142857146</v>
+        <v>69997.962142857141</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC0B6FA-7364-4E5B-95CC-1EAFAB2BD257}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B39C992-3329-4CC6-84F4-655B27DE42FE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="83">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -279,6 +279,9 @@
   </si>
   <si>
     <t>05/23/2026</t>
+  </si>
+  <si>
+    <t>05/25/2026</t>
   </si>
 </sst>
 </file>
@@ -2643,7 +2646,9 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="C13" s="19"/>
+      <c r="C13" s="19" t="s">
+        <v>82</v>
+      </c>
       <c r="D13" s="20" t="s">
         <v>68</v>
       </c>
@@ -2651,22 +2656,27 @@
       <c r="F13" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G13" s="20"/>
+      <c r="G13" s="20">
+        <v>518670633</v>
+      </c>
       <c r="H13" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I13" s="21"/>
+      <c r="I13" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K13" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L13" s="27">
         <f>I13-K13</f>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M13" s="33">
         <f>I13/112</f>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -3187,20 +3197,20 @@
       <c r="G32"/>
       <c r="I32" s="46">
         <f>SUM(I7:I31)</f>
-        <v>7839771.7599999998</v>
+        <v>9176122.7199999988</v>
       </c>
       <c r="J32" s="47"/>
       <c r="K32" s="46">
         <f>SUM(K7:K31)</f>
-        <v>839975.54571428569</v>
+        <v>983156.00571428565</v>
       </c>
       <c r="L32" s="46">
         <f>SUM(L7:L31)</f>
-        <v>6999796.2142857146</v>
+        <v>8192966.7142857146</v>
       </c>
       <c r="M32" s="48">
         <f>SUM(M7:M31)</f>
-        <v>69997.962142857141</v>
+        <v>81929.667142857143</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B39C992-3329-4CC6-84F4-655B27DE42FE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50BF4AC6-7B20-42C8-857F-2DB2A8D6A23D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="84">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -282,6 +282,9 @@
   </si>
   <si>
     <t>05/25/2026</t>
+  </si>
+  <si>
+    <t>05/26/2026</t>
   </si>
 </sst>
 </file>
@@ -2688,7 +2691,9 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="C14" s="19"/>
+      <c r="C14" s="19" t="s">
+        <v>83</v>
+      </c>
       <c r="D14" s="20" t="s">
         <v>68</v>
       </c>
@@ -2696,22 +2701,28 @@
       <c r="F14" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G14" s="20"/>
+      <c r="G14" s="20">
+        <f>518675113</f>
+        <v>518675113</v>
+      </c>
       <c r="H14" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I14" s="37"/>
+      <c r="I14" s="37">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K14" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L14" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M14" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -3197,20 +3208,20 @@
       <c r="G32"/>
       <c r="I32" s="46">
         <f>SUM(I7:I31)</f>
-        <v>9176122.7199999988</v>
+        <v>10512473.68</v>
       </c>
       <c r="J32" s="47"/>
       <c r="K32" s="46">
         <f>SUM(K7:K31)</f>
-        <v>983156.00571428565</v>
+        <v>1126336.4657142856</v>
       </c>
       <c r="L32" s="46">
         <f>SUM(L7:L31)</f>
-        <v>8192966.7142857146</v>
+        <v>9386137.2142857146</v>
       </c>
       <c r="M32" s="48">
         <f>SUM(M7:M31)</f>
-        <v>81929.667142857143</v>
+        <v>93861.372142857144</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50BF4AC6-7B20-42C8-857F-2DB2A8D6A23D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7EF62C4-1137-4413-A17F-7832DF572CF2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="85">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -285,6 +285,9 @@
   </si>
   <si>
     <t>05/26/2026</t>
+  </si>
+  <si>
+    <t>05/27/2026</t>
   </si>
 </sst>
 </file>
@@ -2734,7 +2737,9 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="C15" s="19"/>
+      <c r="C15" s="19" t="s">
+        <v>84</v>
+      </c>
       <c r="D15" s="20" t="s">
         <v>68</v>
       </c>
@@ -2742,22 +2747,27 @@
       <c r="F15" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="20"/>
+      <c r="G15" s="20">
+        <v>518679022</v>
+      </c>
       <c r="H15" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I15" s="21"/>
+      <c r="I15" s="21">
+        <f>1350920-57135.71</f>
+        <v>1293784.29</v>
+      </c>
       <c r="K15" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>138619.74535714288</v>
       </c>
       <c r="L15" s="27">
         <f>I15-K15</f>
-        <v>0</v>
+        <v>1155164.5446428573</v>
       </c>
       <c r="M15" s="33">
         <f>I15/112</f>
-        <v>0</v>
+        <v>11551.645446428573</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -3208,20 +3218,20 @@
       <c r="G32"/>
       <c r="I32" s="46">
         <f>SUM(I7:I31)</f>
-        <v>10512473.68</v>
+        <v>11806257.969999999</v>
       </c>
       <c r="J32" s="47"/>
       <c r="K32" s="46">
         <f>SUM(K7:K31)</f>
-        <v>1126336.4657142856</v>
+        <v>1264956.2110714284</v>
       </c>
       <c r="L32" s="46">
         <f>SUM(L7:L31)</f>
-        <v>9386137.2142857146</v>
+        <v>10541301.758928571</v>
       </c>
       <c r="M32" s="48">
         <f>SUM(M7:M31)</f>
-        <v>93861.372142857144</v>
+        <v>105413.01758928572</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7EF62C4-1137-4413-A17F-7832DF572CF2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E763EE9B-7115-452A-95C6-8F841C151B70}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="86">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -288,6 +288,9 @@
   </si>
   <si>
     <t>05/27/2026</t>
+  </si>
+  <si>
+    <t>05/28/2026</t>
   </si>
 </sst>
 </file>
@@ -2779,7 +2782,9 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="C16" s="19"/>
+      <c r="C16" s="19" t="s">
+        <v>85</v>
+      </c>
       <c r="D16" s="20" t="s">
         <v>68</v>
       </c>
@@ -2787,22 +2792,27 @@
       <c r="F16" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G16" s="20"/>
+      <c r="G16" s="20">
+        <v>518682681</v>
+      </c>
       <c r="H16" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I16" s="21"/>
+      <c r="I16" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K16" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L16" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M16" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -3218,20 +3228,20 @@
       <c r="G32"/>
       <c r="I32" s="46">
         <f>SUM(I7:I31)</f>
-        <v>11806257.969999999</v>
+        <v>13142608.93</v>
       </c>
       <c r="J32" s="47"/>
       <c r="K32" s="46">
         <f>SUM(K7:K31)</f>
-        <v>1264956.2110714284</v>
+        <v>1408136.6710714283</v>
       </c>
       <c r="L32" s="46">
         <f>SUM(L7:L31)</f>
-        <v>10541301.758928571</v>
+        <v>11734472.258928571</v>
       </c>
       <c r="M32" s="48">
         <f>SUM(M7:M31)</f>
-        <v>105413.01758928572</v>
+        <v>117344.72258928572</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E763EE9B-7115-452A-95C6-8F841C151B70}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B40BD2-FAC1-449E-9FC5-5D62B68328D5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="87">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -291,6 +291,9 @@
   </si>
   <si>
     <t>05/28/2026</t>
+  </si>
+  <si>
+    <t>05/29/2026</t>
   </si>
 </sst>
 </file>
@@ -2456,7 +2459,7 @@
         <v>70</v>
       </c>
       <c r="G8" s="20">
-        <v>51864</v>
+        <v>518648050</v>
       </c>
       <c r="H8" s="20" t="s">
         <v>74</v>
@@ -2824,7 +2827,9 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="C17" s="19"/>
+      <c r="C17" s="19" t="s">
+        <v>86</v>
+      </c>
       <c r="D17" s="20" t="s">
         <v>68</v>
       </c>
@@ -2832,22 +2837,27 @@
       <c r="F17" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G17" s="20"/>
+      <c r="G17" s="20">
+        <v>518686700</v>
+      </c>
       <c r="H17" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I17" s="21"/>
+      <c r="I17" s="21">
+        <f>1397196-81220.75</f>
+        <v>1315975.25</v>
+      </c>
       <c r="K17" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>140997.34821428571</v>
       </c>
       <c r="L17" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1174977.9017857143</v>
       </c>
       <c r="M17" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11749.779017857143</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -3228,20 +3238,20 @@
       <c r="G32"/>
       <c r="I32" s="46">
         <f>SUM(I7:I31)</f>
-        <v>13142608.93</v>
+        <v>14458584.18</v>
       </c>
       <c r="J32" s="47"/>
       <c r="K32" s="46">
         <f>SUM(K7:K31)</f>
-        <v>1408136.6710714283</v>
+        <v>1549134.019285714</v>
       </c>
       <c r="L32" s="46">
         <f>SUM(L7:L31)</f>
-        <v>11734472.258928571</v>
+        <v>12909450.160714285</v>
       </c>
       <c r="M32" s="48">
         <f>SUM(M7:M31)</f>
-        <v>117344.72258928572</v>
+        <v>129094.50160714287</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B40BD2-FAC1-449E-9FC5-5D62B68328D5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942F4E01-5F67-4868-B824-36FE9DE05B81}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="88">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -294,6 +294,9 @@
   </si>
   <si>
     <t>05/29/2026</t>
+  </si>
+  <si>
+    <t>05/30/2026</t>
   </si>
 </sst>
 </file>
@@ -2869,7 +2872,9 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="C18" s="19"/>
+      <c r="C18" s="19" t="s">
+        <v>87</v>
+      </c>
       <c r="D18" s="20" t="s">
         <v>68</v>
       </c>
@@ -2877,22 +2882,27 @@
       <c r="F18" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G18" s="20"/>
+      <c r="G18" s="20">
+        <v>518691204</v>
+      </c>
       <c r="H18" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I18" s="21"/>
+      <c r="I18" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K18" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L18" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M18" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -2904,7 +2914,9 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="C19" s="19"/>
+      <c r="C19" s="19" t="s">
+        <v>87</v>
+      </c>
       <c r="D19" s="20" t="s">
         <v>68</v>
       </c>
@@ -2912,22 +2924,27 @@
       <c r="F19" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G19" s="20"/>
+      <c r="G19" s="20">
+        <v>518690654</v>
+      </c>
       <c r="H19" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I19" s="21"/>
+      <c r="I19" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K19" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L19" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M19" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -3238,20 +3255,20 @@
       <c r="G32"/>
       <c r="I32" s="46">
         <f>SUM(I7:I31)</f>
-        <v>14458584.18</v>
+        <v>17131286.100000001</v>
       </c>
       <c r="J32" s="47"/>
       <c r="K32" s="46">
         <f>SUM(K7:K31)</f>
-        <v>1549134.019285714</v>
+        <v>1835494.9392857139</v>
       </c>
       <c r="L32" s="46">
         <f>SUM(L7:L31)</f>
-        <v>12909450.160714285</v>
+        <v>15295791.160714285</v>
       </c>
       <c r="M32" s="48">
         <f>SUM(M7:M31)</f>
-        <v>129094.50160714287</v>
+        <v>152957.91160714286</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
+++ b/GBDS MAY FILES 2026/PURCHASES - MAY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS MAY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942F4E01-5F67-4868-B824-36FE9DE05B81}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7CDBFD-90F1-4A59-B18F-01807A03E130}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="89">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -297,6 +297,9 @@
   </si>
   <si>
     <t>05/30/2026</t>
+  </si>
+  <si>
+    <t>05/31/2026</t>
   </si>
 </sst>
 </file>
@@ -2956,7 +2959,9 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="C20" s="19"/>
+      <c r="C20" s="19" t="s">
+        <v>88</v>
+      </c>
       <c r="D20" s="20" t="s">
         <v>68</v>
       </c>
@@ -2964,22 +2969,27 @@
       <c r="F20" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G20" s="20"/>
+      <c r="G20" s="20">
+        <v>518693847</v>
+      </c>
       <c r="H20" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I20" s="21"/>
+      <c r="I20" s="21">
+        <f>1442734-62199.45</f>
+        <v>1380534.55</v>
+      </c>
       <c r="K20" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>147914.41607142857</v>
       </c>
       <c r="L20" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1232620.1339285714</v>
       </c>
       <c r="M20" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12326.201339285715</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -2991,7 +3001,9 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="C21" s="19"/>
+      <c r="C21" s="19" t="s">
+        <v>88</v>
+      </c>
       <c r="D21" s="20" t="s">
         <v>68</v>
       </c>
@@ -2999,22 +3011,27 @@
       <c r="F21" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G21" s="20"/>
+      <c r="G21" s="20">
+        <v>518693763</v>
+      </c>
       <c r="H21" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I21" s="21"/>
+      <c r="I21" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K21" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L21" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M21" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -3026,7 +3043,9 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="C22" s="19"/>
+      <c r="C22" s="19" t="s">
+        <v>88</v>
+      </c>
       <c r="D22" s="20" t="s">
         <v>68</v>
       </c>
@@ -3034,22 +3053,27 @@
       <c r="F22" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G22" s="20"/>
+      <c r="G22" s="20">
+        <v>518693766</v>
+      </c>
       <c r="H22" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I22" s="21"/>
+      <c r="I22" s="21">
+        <f>1643760-71582.4</f>
+        <v>1572177.6</v>
+      </c>
       <c r="K22" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>168447.6</v>
       </c>
       <c r="L22" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1403730</v>
       </c>
       <c r="M22" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>14037.300000000001</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -3255,20 +3279,20 @@
       <c r="G32"/>
       <c r="I32" s="46">
         <f>SUM(I7:I31)</f>
-        <v>17131286.100000001</v>
+        <v>21420349.210000005</v>
       </c>
       <c r="J32" s="47"/>
       <c r="K32" s="46">
         <f>SUM(K7:K31)</f>
-        <v>1835494.9392857139</v>
+        <v>2295037.4153571427</v>
       </c>
       <c r="L32" s="46">
         <f>SUM(L7:L31)</f>
-        <v>15295791.160714285</v>
+        <v>19125311.794642858</v>
       </c>
       <c r="M32" s="48">
         <f>SUM(M7:M31)</f>
-        <v>152957.91160714286</v>
+        <v>191253.11794642854</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
